--- a/artfynd/A 49809-2023 artfynd.xlsx
+++ b/artfynd/A 49809-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49809-2023 artfynd.xlsx
+++ b/artfynd/A 49809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112607010</v>
+        <v>112610507</v>
       </c>
       <c r="B13" t="n">
-        <v>91018</v>
+        <v>88398</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,38 +1934,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Norriån, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>805690</v>
+        <v>805687</v>
       </c>
       <c r="R13" t="n">
-        <v>7355647</v>
+        <v>7355667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112607012</v>
+        <v>112610508</v>
       </c>
       <c r="B14" t="n">
         <v>91024</v>
@@ -2065,14 +2065,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Norriån, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>805696</v>
+        <v>805687</v>
       </c>
       <c r="R14" t="n">
-        <v>7355667</v>
+        <v>7355665</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,327 +2133,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112610507</v>
-      </c>
-      <c r="B15" t="n">
-        <v>88398</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>6276</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Tricholoma matsutake</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Norriån, Nb</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>805687</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7355667</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112610508</v>
-      </c>
-      <c r="B16" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hydnellum aurantiacum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Norriån, Nb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>805687</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7355665</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>112607011</v>
-      </c>
-      <c r="B17" t="n">
-        <v>88398</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6276</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Tricholoma matsutake</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>805687</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7355665</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49809-2023 artfynd.xlsx
+++ b/artfynd/A 49809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104160493</v>
+        <v>112610503</v>
       </c>
       <c r="B2" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Norriån, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>805686.9305882088</v>
+        <v>805774</v>
       </c>
       <c r="R2" t="n">
-        <v>7355664.558264034</v>
+        <v>7355409</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104160492</v>
+        <v>112607010</v>
       </c>
       <c r="B3" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,12 +797,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>805690.1134799146</v>
+        <v>805690</v>
       </c>
       <c r="R3" t="n">
-        <v>7355646.572715294</v>
+        <v>7355647</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104160494</v>
+        <v>112610506</v>
       </c>
       <c r="B4" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Norriån, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>805695.6660502276</v>
+        <v>805688</v>
       </c>
       <c r="R4" t="n">
-        <v>7355666.732090874</v>
+        <v>7355648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +947,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109910110</v>
+        <v>112183395</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,37 +992,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norriån, Nb</t>
+          <t>Valvträsk, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>805687.9666456764</v>
+        <v>805672</v>
       </c>
       <c r="R5" t="n">
-        <v>7355647.56099094</v>
+        <v>7355620</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,27 +1050,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109910112</v>
+        <v>112607012</v>
       </c>
       <c r="B6" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,34 +1098,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norriån, Nb</t>
+          <t>Valvträsk, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>805686.71128431</v>
+        <v>805696</v>
       </c>
       <c r="R6" t="n">
-        <v>7355666.571287565</v>
+        <v>7355667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,19 +1155,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1260,15 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112183395</v>
+        <v>112610508</v>
       </c>
       <c r="B7" t="n">
-        <v>90845</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,24 +1217,20 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valvträsk, Nb</t>
+          <t>Norriån, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>805672</v>
+        <v>805687</v>
       </c>
       <c r="R7" t="n">
-        <v>7355621</v>
+        <v>7355664</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,17 +1254,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112192876</v>
+        <v>112182423</v>
       </c>
       <c r="B8" t="n">
-        <v>90896</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1415,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>805658</v>
+        <v>805662</v>
       </c>
       <c r="R8" t="n">
-        <v>7355657</v>
+        <v>7355650</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1485,16 +1400,11 @@
         <v>112183528</v>
       </c>
       <c r="B9" t="n">
-        <v>90865</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1529,7 +1439,7 @@
         <v>805677</v>
       </c>
       <c r="R9" t="n">
-        <v>7355624</v>
+        <v>7355623</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1593,15 +1503,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112182423</v>
+        <v>112183530</v>
       </c>
       <c r="B10" t="n">
-        <v>90847</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,21 +1514,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1637,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>805662</v>
+        <v>805661</v>
       </c>
       <c r="R10" t="n">
-        <v>7355650</v>
+        <v>7355641</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,37 +1609,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112183712</v>
+        <v>112192876</v>
       </c>
       <c r="B11" t="n">
-        <v>96795</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>5448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1748,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>805600</v>
+        <v>805658</v>
       </c>
       <c r="R11" t="n">
-        <v>7355651</v>
+        <v>7355657</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1778,12 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1815,50 +1715,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112610506</v>
+        <v>112607011</v>
       </c>
       <c r="B12" t="n">
-        <v>91018</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norriån, Nb</t>
+          <t>Valvträsk, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>805688</v>
+        <v>805687</v>
       </c>
       <c r="R12" t="n">
-        <v>7355648</v>
+        <v>7355664</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,12 +1820,7 @@
         <v>112610507</v>
       </c>
       <c r="B13" t="n">
-        <v>88398</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2029,15 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112610508</v>
+        <v>112183215</v>
       </c>
       <c r="B14" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2045,37 +1930,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norriån, Nb</t>
+          <t>Valvträsk, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>805687</v>
+        <v>805750</v>
       </c>
       <c r="R14" t="n">
-        <v>7355665</v>
+        <v>7355411</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,17 +1988,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2022,324 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112183058</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>805705</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7355392</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113888172</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>805712</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7355383</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112183712</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>805600</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7355652</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49809-2023 artfynd.xlsx
+++ b/artfynd/A 49809-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610506</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183395</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607012</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610508</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182423</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183528</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183530</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112192876</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610507</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183215</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183058</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2234,6 +2309,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888172</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,8 +2420,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112183712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>